--- a/docs/DOH_기준치_설계근거.xlsx
+++ b/docs/DOH_기준치_설계근거.xlsx
@@ -7,11 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="판정 기준 (17규칙 20구간)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="판정 기준 (18규칙 21구간)" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="42개 커버리지" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'판정 기준 (17규칙 20구간)'!$A$1:$L$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'판정 기준 (18규칙 21구간)'!$A$1:$L$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'42개 커버리지'!$A$1:$E$43</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -543,7 +543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L24"/>
+  <dimension ref="A1:L25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -806,42 +806,42 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>리버스 스파인</t>
+          <t>어드레스 어깨 기울기 부족</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>VF036</t>
+          <t>VF008</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>척추 좌우기울기 @P4 (°, −=타깃쪽 역기울기)</t>
+          <t>어깨 기울기 @P1 (°, +=트레일 어깨가 낮음)</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>음수 클수록</t>
+          <t>작을수록 나쁨</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>≥−5</t>
+          <t>≥5</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>−5~−10</t>
+          <t>2~5</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>−10~−18</t>
+          <t>0~2</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>≤−18</t>
+          <t>≤0</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -859,24 +859,24 @@
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>코칭 관행: 탑에서 척추 5° 이상 타깃쪽 역기울기부터 주시</t>
+          <t>오른손잡이는 트레일 손이 그립 아래라 트레일 어깨가 낮은 게 정상 — 코칭 통설 8~12°(클럽 길이·그립에 따라 변동). 0° 이하는 트레일 어깨가 오히려 높다는 뜻이라 기하학적으로 명백한 이상(여기만 사실상 A급 확실). 하한 5°는 selfcheck_metrics.py 실측: up축 '전두면 롤' 오차가 1:1로 전파되므로(시상면 오차는 거의 무영향) 그 여유분. KB `Shoulder Height Trail High (P1)` = 원인 5·결과 0 의 순수 뿌리원인 노드</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>힙 슬라이드 과다</t>
+          <t>리버스 스파인</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>VF091</t>
+          <t>VF036</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>골반 좌우이동 P4→P7 (−=리드쪽)</t>
+          <t>척추 좌우기울기 @P4 (°, −=타깃쪽 역기울기)</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -886,22 +886,22 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>≥−0.35</t>
+          <t>≥−5</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>−0.35~−0.45</t>
+          <t>−5~−10</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>−0.45~−0.60</t>
+          <t>−10~−18</t>
         </is>
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>≤−0.60</t>
+          <t>≤−18</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
@@ -912,56 +912,56 @@
       <c r="J6" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="K6" s="8" t="inlineStr">
-        <is>
-          <t>C</t>
+      <c r="K6" s="9" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>임의 seed — 정상 다운스윙도 리드쪽 0.1~0.3 이동하므로 하한 넉넉히</t>
+          <t>코칭 관행: 탑에서 척추 5° 이상 타깃쪽 역기울기부터 주시</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>행잉백</t>
+          <t>힙 슬라이드 과다</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>VF085</t>
+          <t>VF091</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>골반 위치 @P7 vs P1 (+=트레일 잔류)</t>
+          <t>골반 좌우이동 P4→P7 (−=리드쪽)</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>클수록 나쁨</t>
+          <t>음수 클수록</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>≤0.06</t>
+          <t>≥−0.35</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>0.06~0.12</t>
+          <t>−0.35~−0.45</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>0.12~0.20</t>
+          <t>−0.45~−0.60</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>≥0.20</t>
+          <t>≤−0.60</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -979,89 +979,89 @@
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>임의 seed</t>
+          <t>임의 seed — 정상 다운스윙도 리드쪽 0.1~0.3 이동하므로 하한 넉넉히</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>자세 무너짐</t>
+          <t>행잉백</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>VF038</t>
+          <t>VF085</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>척추각 변화 P1→P4 (°, |Δ|)</t>
+          <t>골반 위치 @P7 vs P1 (+=트레일 잔류)</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>|값| 클수록</t>
+          <t>클수록 나쁨</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>≤8</t>
+          <t>≤0.06</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>8~12</t>
+          <t>0.06~0.12</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>12~18</t>
+          <t>0.12~0.20</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>≥18</t>
+          <t>≥0.20</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>측면</t>
+          <t>정면</t>
         </is>
       </c>
       <c r="J8" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="K8" s="9" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="K8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>코칭 관행: 백스윙 중 자세각 ±5~10° 유지가 통설</t>
+          <t>임의 seed</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>일어남(임팩트)</t>
+          <t>자세 무너짐</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>VF076</t>
+          <t>VF038</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>척추각 변화 P1→P7 (°, +=일어섬)</t>
+          <t>척추각 변화 P1→P4 (°, |Δ|)</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>클수록 나쁨</t>
+          <t>|값| 클수록</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -1099,24 +1099,24 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>상동</t>
+          <t>코칭 관행: 백스윙 중 자세각 ±5~10° 유지가 통설</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>치킨윙 경향</t>
+          <t>일어남(임팩트)</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>VF087</t>
+          <t>VF076</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>리드팔 굽힘각 @P7 (°, 0=쭉 폄)</t>
+          <t>척추각 변화 P1→P7 (°, +=일어섬)</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -1126,27 +1126,27 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>≤25</t>
+          <t>≤8</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>25~35</t>
+          <t>8~12</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>35~45</t>
+          <t>12~18</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>≥45</t>
+          <t>≥18</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>둘다</t>
+          <t>측면</t>
         </is>
       </c>
       <c r="J10" s="3" t="n">
@@ -1159,24 +1159,24 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>GPT 협의 2차(07-24): 아마추어 분포 18~34° 넓음 + 측정오차 ±3~5° 감안 → 35°부터 과다 (33°는 주의)</t>
+          <t>상동</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>플라잉 엘보 경향</t>
+          <t>치킨윙 경향</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>VF026</t>
+          <t>VF087</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>트레일 팔꿈치 높이 @P4 (상완길이 비율, +=어깨 위)</t>
+          <t>리드팔 굽힘각 @P7 (°, 0=쭉 폄)</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -1186,22 +1186,22 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>≤0.15</t>
+          <t>≤25</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>0.15~0.25</t>
+          <t>25~35</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>0.25~0.40</t>
+          <t>35~45</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>≥0.40</t>
+          <t>≥45</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -1219,49 +1219,49 @@
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>GPT 지적 반영. UI는 "상완의 30%"로 표시. 단일 지표 근사 — M505(팔꿈치 깊이)·M403/404(어깨들림) 구현 후 다중측정 조합 예정</t>
+          <t>GPT 협의 2차(07-24): 아마추어 분포 18~34° 넓음 + 측정오차 ±3~5° 감안 → 35°부터 과다 (33°는 주의)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>오버스윙 경향</t>
+          <t>플라잉 엘보 경향</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>VF123</t>
+          <t>VF026</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>리드팔 수직각 @P4 (°, 작을수록 팔 높음)</t>
+          <t>트레일 팔꿈치 높이 @P4 (상완길이 비율, +=어깨 위)</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>작을수록 나쁨</t>
+          <t>클수록 나쁨</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>≥40</t>
+          <t>≤0.15</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>30~40</t>
+          <t>0.15~0.25</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>20~30</t>
+          <t>0.25~0.40</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>≤20</t>
+          <t>≥0.40</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
@@ -1272,56 +1272,56 @@
       <c r="J12" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="K12" s="8" t="inlineStr">
-        <is>
-          <t>C</t>
+      <c r="K12" s="9" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>단일 프록시 — 정식 오버스윙은 손위치·샤프트·리드암·코킹 4요소 종합(클럽검출 후). 그래서 이름도 "경향"</t>
+          <t>GPT 지적 반영. UI는 "상완의 30%"로 표시. 단일 지표 근사 — M505(팔꿈치 깊이)·M403/404(어깨들림) 구현 후 다중측정 조합 예정</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>상체 회전 부족</t>
+          <t>오버스윙 경향</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>VF015</t>
+          <t>VF123</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>어깨 회전각 @P4 (°, |값|)</t>
+          <t>리드팔 수직각 @P4 (°, 작을수록 팔 높음)</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>|값| 작을수록</t>
+          <t>작을수록 나쁨</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>≥80</t>
+          <t>≥40</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>70~80</t>
+          <t>30~40</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>60~70</t>
+          <t>20~30</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>≤60</t>
+          <t>≤20</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -1332,56 +1332,56 @@
       <c r="J13" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="K13" s="9" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="K13" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>측정명(어깨 회전각)과 진단명(상체 회전 부족) 분리. 통상 어깨턴 85~105° 기반. ⚠️스케일 보정전</t>
+          <t>단일 프록시 — 정식 오버스윙은 손위치·샤프트·리드암·코킹 4요소 종합(클럽검출 후). 그래서 이름도 "경향"</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>X-Factor 이상(과대)</t>
+          <t>상체 회전 부족</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>VF020</t>
+          <t>VF015</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>X-Factor @P4 (°, |값|)</t>
+          <t>어깨 회전각 @P4 (°, |값|)</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>|값| 클수록</t>
+          <t>|값| 작을수록</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>25~50</t>
+          <t>≥80</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>50~60 (큼)</t>
+          <t>70~80</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>≥60 (과대)</t>
+          <t>60~70</t>
         </is>
       </c>
       <c r="H14" s="7" t="inlineStr">
         <is>
-          <t>— (최고단계=과대)</t>
+          <t>≤60</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
@@ -1399,14 +1399,14 @@
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>GPT 협의(07-24): 아마 35~45 / 좋은 선수 40~55 / 60↑ 과다. 이 지표의 최고 단계는 "과대"로 정의(스케일 보정 전 심함 단계 안 둠)</t>
+          <t>측정명(어깨 회전각)과 진단명(상체 회전 부족) 분리. 통상 어깨턴 85~105° 기반. ⚠️스케일 보정전</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>X-Factor 이상(부족)</t>
+          <t>X-Factor 이상(과대)</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -1421,27 +1421,27 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>|값| 작을수록</t>
+          <t>|값| 클수록</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>≥25</t>
+          <t>25~50</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>&lt;25 (부족)</t>
+          <t>50~60 (큼)</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>≥60 (과대)</t>
         </is>
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>— (최고단계=과대)</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -1459,49 +1459,49 @@
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>분리각 25° 미만이면 파워 손실 신호(주의만)</t>
+          <t>GPT 협의(07-24): 아마 35~45 / 좋은 선수 40~55 / 60↑ 과다. 이 지표의 최고 단계는 "과대"로 정의(스케일 보정 전 심함 단계 안 둠)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>트레일 무릎 펴짐</t>
+          <t>X-Factor 이상(부족)</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>VF040</t>
+          <t>VF020</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>트레일 무릎 굽힘 @P4 (°, 0=곧음)</t>
+          <t>X-Factor @P4 (°, |값|)</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>작을수록 나쁨</t>
+          <t>|값| 작을수록</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>≥12</t>
+          <t>≥25</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>8~12</t>
+          <t>&lt;25 (부족)</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>4~8</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H16" s="7" t="inlineStr">
         <is>
-          <t>≤4</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
@@ -1512,56 +1512,56 @@
       <c r="J16" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="K16" s="8" t="inlineStr">
-        <is>
-          <t>C</t>
+      <c r="K16" s="9" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>임의 seed — 탑에서 굽힘 유지 12°+ 를 이상으로 가정</t>
+          <t>분리각 25° 미만이면 파워 손실 신호(주의만)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>머리 상하 출렁</t>
+          <t>트레일 무릎 펴짐</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>VF033</t>
+          <t>VF040</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>머리 상하이동 P1→P4 (스탠스폭 비율, |Δ|)</t>
+          <t>트레일 무릎 굽힘 @P4 (°, 0=곧음)</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>|값| 클수록</t>
+          <t>작을수록 나쁨</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>≤0.12</t>
+          <t>≥12</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>0.12~0.18</t>
+          <t>8~12</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>0.18~0.28</t>
+          <t>4~8</t>
         </is>
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>≥0.28</t>
+          <t>≤4</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
@@ -1579,49 +1579,49 @@
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
-          <t>임의 seed</t>
+          <t>임의 seed — 탑에서 굽힘 유지 12°+ 를 이상으로 가정</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>템포(느림)</t>
+          <t>머리 상하 출렁</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>VF111</t>
+          <t>VF033</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>백:다운 시간비</t>
+          <t>머리 상하이동 P1→P4 (스탠스폭 비율, |Δ|)</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>클수록(3.6+)</t>
+          <t>|값| 클수록</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>≤3.6</t>
+          <t>≤0.12</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>3.6~4.2</t>
+          <t>0.12~0.18</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>4.2~5.0</t>
+          <t>0.18~0.28</t>
         </is>
       </c>
       <c r="H18" s="7" t="inlineStr">
         <is>
-          <t>≥5.0</t>
+          <t>≥0.28</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
@@ -1632,21 +1632,21 @@
       <c r="J18" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="K18" s="9" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="K18" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>3:1 통설(Tour Tempo) 중심 ±여유</t>
+          <t>임의 seed</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>템포(빠름)</t>
+          <t>템포(느림)</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1661,27 +1661,27 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>작을수록(2.2−)</t>
+          <t>클수록(3.6+)</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>≥2.2</t>
+          <t>≤3.6</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>1.8~2.2</t>
+          <t>3.6~4.2</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>1.4~1.8</t>
+          <t>4.2~5.0</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>≤1.4</t>
+          <t>≥5.0</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
@@ -1699,84 +1699,84 @@
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
-          <t>상동</t>
+          <t>3:1 통설(Tour Tempo) 중심 ±여유</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>얼리 익스텐션</t>
+          <t>템포(빠름)</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>VF067</t>
+          <t>VF111</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>골반 볼쪽 이동 P5→P7 (스탠스폭 비율)</t>
+          <t>백:다운 시간비</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>클수록 나쁨</t>
+          <t>작을수록(2.2−)</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>≤0.10</t>
+          <t>≥2.2</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>0.10~0.15</t>
+          <t>1.8~2.2</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>0.15~0.25</t>
+          <t>1.4~1.8</t>
         </is>
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
-          <t>≥0.25</t>
+          <t>≤1.4</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>측면</t>
+          <t>둘다</t>
         </is>
       </c>
       <c r="J20" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="K20" s="8" t="inlineStr">
-        <is>
-          <t>C</t>
+        <v>1</v>
+      </c>
+      <c r="K20" s="9" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>임의 seed + 깊이추정(오차 큼) — 반드시 실측 보정</t>
+          <t>상동</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>오버더톱 경향</t>
+          <t>얼리 익스텐션</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>VF059</t>
+          <t>VF067</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>손 깊이변화 P4→P6 (스탠스폭 비율, +=볼쪽)</t>
+          <t>골반 볼쪽 이동 P5→P7 (스탠스폭 비율)</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -1786,22 +1786,22 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>≤0.20</t>
+          <t>≤0.10</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>0.20~0.30</t>
+          <t>0.10~0.15</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>0.30~0.45</t>
+          <t>0.15~0.25</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>≥0.45</t>
+          <t>≥0.25</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
@@ -1819,29 +1819,89 @@
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
+          <t>임의 seed + 깊이추정(오차 큼) — 반드시 실측 보정</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>오버더톱 경향</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>VF059</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>손 깊이변화 P4→P6 (스탠스폭 비율, +=볼쪽)</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>클수록 나쁨</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>≤0.20</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>0.20~0.30</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>0.30~0.45</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>≥0.45</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>측면</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K22" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L22" s="4" t="inlineStr">
+        <is>
           <t>임의 seed + 깊이추정</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="10" t="inlineStr">
-        <is>
-          <t>근거 등급 정의 — A: 논문·투어 데이터로 검증된 값(현재 0개, 최종 목표) / B: 코칭 컨센서스·업계 통용 수치·검수 협의 기반 추정 / C: Seed(임의 가정, 실측으로 대체 예정). 모든 구간은 실측 스윙이 쌓이면 평균±표준편차 기반으로 재설정 예정.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
+          <t>근거 등급 정의 — A: 논문·투어 데이터로 검증된 값(현재 0개, 최종 목표) / B: 코칭 컨센서스·업계 통용 수치·검수 협의 기반 추정 / C: Seed(임의 가정, 실측으로 대체 예정). 모든 구간은 실측 스윙이 쌓이면 평균±표준편차 기반으로 재설정 예정.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
           <t>판정 로직: 4단계 구간. 명명 원칙(검수 2차 반영): 측정명(Feature, 예: 어깨 회전각)과 진단명(예: 상체 회전 부족)을 분리하고, 단일 지표 근사 진단엔 '경향'을 붙인다. 다중측정→한 문제 조합은 DOH Node 설계(계약 §3.6)가 최종 형태 — 측정이 채워지면 규칙에 check만 추가.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L21"/>
+  <autoFilter ref="A1:L22"/>
   <mergeCells count="2">
     <mergeCell ref="A24:L24"/>
-    <mergeCell ref="A23:L23"/>
+    <mergeCell ref="A25:L25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2259,12 +2319,16 @@
       <c r="C17" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="16" t="inlineStr">
-        <is>
-          <t>미구현</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr"/>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
+          <t>규칙 있음</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>어드레스 어깨 기울기 부족 (VF008@P1, 정면). 단위는 deg — M402와 같은 정보의 두 표현이라 각도로 통일(상용 Side Bend 대조용)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
@@ -2851,7 +2915,7 @@
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>합계 42: 판정 규칙 연결 13 · 측정만(기준 미설정) 6 · 미구현 23. '측정만'은 값은 나오지만 정상/문제 구간이 아직 없는 것 — 기준 추가 후보.</t>
+          <t>합계 42: 판정 규칙 연결 14 · 측정만(기준 미설정) 6 · 미구현 22. '측정만'은 값은 나오지만 정상/문제 구간이 아직 없는 것 — 기준 추가 후보.</t>
         </is>
       </c>
     </row>

--- a/docs/DOH_기준치_설계근거.xlsx
+++ b/docs/DOH_기준치_설계근거.xlsx
@@ -1893,7 +1893,7 @@
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>판정 로직: 4단계 구간. 명명 원칙(검수 2차 반영): 측정명(Feature, 예: 어깨 회전각)과 진단명(예: 상체 회전 부족)을 분리하고, 단일 지표 근사 진단엔 '경향'을 붙인다. 다중측정→한 문제 조합은 DOH Node 설계(계약 §3.6)가 최종 형태 — 측정이 채워지면 규칙에 check만 추가.</t>
+          <t>판정 로직: 4단계 구간. ⚠️ 경계 규약: 경계값에 정확히 걸리면 나쁜 쪽 판정(보수적) — 이 표의 ≤0.12 는 동작상 &lt;0.12 (analyzer2 v36부터 화면 문구도 &gt;/&lt; 로 일치시킴). 명명 원칙(검수 2차 반영): 측정명(Feature, 예: 어깨 회전각)과 진단명(예: 상체 회전 부족)을 분리하고, 단일 지표 근사 진단엔 '경향'을 붙인다. 다중측정→한 문제 조합은 DOH Node 설계(계약 §3.6)가 최종 형태 — 측정이 채워지면 규칙에 check만 추가.</t>
         </is>
       </c>
     </row>
